--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -943,10 +943,10 @@
     <t>0.0003,0.0000,0.0028,0.9991</t>
   </si>
   <si>
-    <t>0.0002,0.0000,0.5505,0.6408</t>
-  </si>
-  <si>
-    <t>0.0043,0.0042,0.6565,0.2076</t>
+    <t>0.0002,0.0000,0.5506,0.6408</t>
+  </si>
+  <si>
+    <t>0.0043,0.0042,0.6566,0.2076</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.8223,0.3552</t>
@@ -1381,7 +1381,7 @@
     <t>0.0007,0.0000,0.0189,0.9893</t>
   </si>
   <si>
-    <t>0.0010,0.0000,0.0576,0.9704</t>
+    <t>0.0010,0.0000,0.0577,0.9704</t>
   </si>
   <si>
     <t>0.0022,0.0000,0.0151,0.9937</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -817,7 +817,7 @@
     <t>0,0,1,1</t>
   </si>
   <si>
-    <t>1,0,0,0</t>
+    <t>0,0,0,0</t>
   </si>
   <si>
     <t>0.0010,0.0000,0.0154,0.9947</t>
@@ -862,10 +862,10 @@
     <t>0.0010,0.0000,0.0178,0.9875</t>
   </si>
   <si>
-    <t>0.0015,0.0000,0.0580,0.9243</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.1511,0.8549</t>
+    <t>0.0015,0.0000,0.0579,0.9244</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.1511,0.8551</t>
   </si>
   <si>
     <t>0.0049,0.0000,0.0022,0.9914</t>
@@ -883,7 +883,7 @@
     <t>0.0055,0.0000,0.0011,0.9963</t>
   </si>
   <si>
-    <t>0.0124,0.0038,0.1169,0.9550</t>
+    <t>0.0124,0.0038,0.1168,0.9551</t>
   </si>
   <si>
     <t>0.0007,0.0000,0.0041,0.9963</t>
@@ -892,19 +892,19 @@
     <t>0.0003,0.0000,0.0351,0.9761</t>
   </si>
   <si>
-    <t>0.0004,0.0000,0.0927,0.8817</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0548,0.9605</t>
+    <t>0.0004,0.0000,0.0926,0.8819</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0548,0.9606</t>
   </si>
   <si>
     <t>0.0011,0.0000,0.0128,0.9862</t>
   </si>
   <si>
-    <t>0.0003,0.0000,0.1133,0.8829</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.5490,0.4727</t>
+    <t>0.0003,0.0000,0.1132,0.8830</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.5489,0.4730</t>
   </si>
   <si>
     <t>0.0035,0.0000,0.0027,0.9957</t>
@@ -916,7 +916,7 @@
     <t>0.0019,0.0000,0.0065,0.9898</t>
   </si>
   <si>
-    <t>0.0026,0.0000,0.0264,0.9822</t>
+    <t>0.0026,0.0000,0.0263,0.9822</t>
   </si>
   <si>
     <t>0.0030,0.0000,0.0004,0.9983</t>
@@ -937,19 +937,19 @@
     <t>0.0000,0.0000,0.9965,0.0033</t>
   </si>
   <si>
-    <t>0.0001,0.0000,0.8690,0.1341</t>
+    <t>0.0001,0.0000,0.8688,0.1344</t>
   </si>
   <si>
     <t>0.0003,0.0000,0.0028,0.9991</t>
   </si>
   <si>
-    <t>0.0002,0.0000,0.5506,0.6408</t>
-  </si>
-  <si>
-    <t>0.0043,0.0042,0.6566,0.2076</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.8223,0.3552</t>
+    <t>0.0002,0.0000,0.5504,0.6412</t>
+  </si>
+  <si>
+    <t>0.0043,0.0042,0.6565,0.2078</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.8222,0.3556</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0002,0.9999</t>
@@ -958,28 +958,28 @@
     <t>0.0019,0.0899,0.0138,0.9937</t>
   </si>
   <si>
-    <t>0.0116,0.1911,0.1241,0.8677</t>
-  </si>
-  <si>
-    <t>0.0106,0.1947,0.0985,0.9277</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.8609,0.2870</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.6189,0.5578</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.3690,0.6271</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0533,0.8985</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.3131,0.6576</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.1868,0.8589</t>
+    <t>0.0116,0.1912,0.1241,0.8677</t>
+  </si>
+  <si>
+    <t>0.0106,0.1947,0.0984,0.9278</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.8609,0.2871</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.6188,0.5581</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.3689,0.6275</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.0533,0.8986</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.3130,0.6578</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.1867,0.8591</t>
   </si>
   <si>
     <t>0.0014,0.0000,0.0002,0.9994</t>
@@ -1003,13 +1003,13 @@
     <t>0.0066,0.0000,0.0004,0.9969</t>
   </si>
   <si>
-    <t>0.0001,0.0005,0.8935,0.1502</t>
+    <t>0.0001,0.0005,0.8935,0.1504</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9916,0.0070</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.9280,0.1314</t>
+    <t>0.0000,0.0000,0.9279,0.1316</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.9885,0.0069</t>
@@ -1039,10 +1039,10 @@
     <t>0.0001,0.0000,0.9924,0.0037</t>
   </si>
   <si>
-    <t>0.0005,0.0106,0.8203,0.1308</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.7299,0.4156</t>
+    <t>0.0005,0.0107,0.8203,0.1308</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.7299,0.4158</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0001,1.0000</t>
@@ -1054,22 +1054,22 @@
     <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0002,0.8352,0.2606</t>
+    <t>0.0002,0.0002,0.8351,0.2609</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9839,0.0135</t>
   </si>
   <si>
-    <t>0.0002,0.0000,0.6530,0.4740</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.8657,0.2260</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9696,0.0223</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.4002,0.8123</t>
+    <t>0.0002,0.0000,0.6529,0.4743</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.8656,0.2263</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9696,0.0224</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.4000,0.8125</t>
   </si>
   <si>
     <t>0.0008,0.0000,0.0002,0.9998</t>
@@ -1090,7 +1090,7 @@
     <t>0.0021,0.0000,0.0003,0.9990</t>
   </si>
   <si>
-    <t>0.0763,0.0010,0.6174,0.0555</t>
+    <t>0.0762,0.0010,0.6175,0.0556</t>
   </si>
   <si>
     <t>0.0018,0.0000,0.0002,0.9994</t>
@@ -1108,7 +1108,7 @@
     <t>0.0011,0.0000,0.0002,0.9996</t>
   </si>
   <si>
-    <t>0.0180,0.0001,0.0634,0.8707</t>
+    <t>0.0180,0.0001,0.0634,0.8710</t>
   </si>
   <si>
     <t>0.0009,0.0000,0.0001,0.9998</t>
@@ -1117,7 +1117,7 @@
     <t>0.0041,0.0000,0.0003,0.9983</t>
   </si>
   <si>
-    <t>0.0001,0.0000,0.2666,0.7295</t>
+    <t>0.0001,0.0000,0.2665,0.7298</t>
   </si>
   <si>
     <t>0.0019,0.0000,0.0207,0.9647</t>
@@ -1126,7 +1126,7 @@
     <t>0.0006,0.0000,0.0070,0.9923</t>
   </si>
   <si>
-    <t>0.0004,0.0000,0.0469,0.9613</t>
+    <t>0.0004,0.0000,0.0469,0.9614</t>
   </si>
   <si>
     <t>0.0048,0.0001,0.0009,0.9979</t>
@@ -1153,34 +1153,34 @@
     <t>0.0015,0.0000,0.0067,0.9944</t>
   </si>
   <si>
-    <t>0.0004,0.0000,0.0508,0.9710</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.0258,0.9820</t>
+    <t>0.0004,0.0000,0.0508,0.9711</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0258,0.9821</t>
   </si>
   <si>
     <t>0.0009,0.0000,0.0034,0.9976</t>
   </si>
   <si>
-    <t>0.0004,0.0000,0.2015,0.9739</t>
+    <t>0.0004,0.0000,0.2013,0.9740</t>
   </si>
   <si>
     <t>0.0038,0.1234,0.0278,0.9832</t>
   </si>
   <si>
-    <t>0.0042,0.1001,0.0222,0.9858</t>
+    <t>0.0042,0.1002,0.0222,0.9858</t>
   </si>
   <si>
     <t>0.0021,0.0001,0.0022,0.9985</t>
   </si>
   <si>
-    <t>0.0060,0.2662,0.1164,0.8653</t>
-  </si>
-  <si>
-    <t>0.0107,0.0009,0.0166,0.9835</t>
-  </si>
-  <si>
-    <t>0.0026,0.0000,0.0008,0.9985</t>
+    <t>0.0060,0.2663,0.1164,0.8654</t>
+  </si>
+  <si>
+    <t>0.0106,0.0009,0.0165,0.9836</t>
+  </si>
+  <si>
+    <t>0.0026,0.0000,0.0008,0.9986</t>
   </si>
   <si>
     <t>0.0037,0.0000,0.0009,0.9979</t>
@@ -1195,10 +1195,10 @@
     <t>0.0008,0.0000,0.0002,0.9997</t>
   </si>
   <si>
-    <t>0.0029,0.0000,0.0004,0.9984</t>
-  </si>
-  <si>
-    <t>0.0069,0.0001,0.0846,0.9384</t>
+    <t>0.0028,0.0000,0.0004,0.9984</t>
+  </si>
+  <si>
+    <t>0.0068,0.0001,0.0845,0.9385</t>
   </si>
   <si>
     <t>0.0032,0.0000,0.0005,0.9983</t>
@@ -1210,7 +1210,7 @@
     <t>0.0050,0.0000,0.0003,0.9978</t>
   </si>
   <si>
-    <t>0.0002,0.0000,0.6895,0.4575</t>
+    <t>0.0002,0.0000,0.6893,0.4579</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9880,0.0086</t>
@@ -1219,7 +1219,7 @@
     <t>0.0000,0.0000,0.9972,0.0015</t>
   </si>
   <si>
-    <t>0.0001,0.0000,0.6927,0.2278</t>
+    <t>0.0001,0.0000,0.6926,0.2280</t>
   </si>
   <si>
     <t>0.0024,0.0000,0.0014,0.9968</t>
@@ -1228,7 +1228,7 @@
     <t>0.0015,0.0000,0.0037,0.9965</t>
   </si>
   <si>
-    <t>0.0007,0.0000,0.0856,0.9367</t>
+    <t>0.0007,0.0000,0.0856,0.9368</t>
   </si>
   <si>
     <t>0.0017,0.0000,0.0141,0.9894</t>
@@ -1237,7 +1237,7 @@
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0002,0.6228,0.6244</t>
+    <t>0.0002,0.0002,0.6226,0.6247</t>
   </si>
   <si>
     <t>0.0022,0.0000,0.0002,0.9992</t>
@@ -1258,7 +1258,7 @@
     <t>0.1040,0.0001,0.5106,0.0076</t>
   </si>
   <si>
-    <t>0.3223,0.0001,0.0266,0.1450</t>
+    <t>0.3225,0.0001,0.0266,0.1449</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9941,0.0010</t>
@@ -1267,7 +1267,7 @@
     <t>0.0634,0.0000,0.0017,0.9369</t>
   </si>
   <si>
-    <t>0.0234,0.0000,0.0020,0.9792</t>
+    <t>0.0233,0.0000,0.0020,0.9792</t>
   </si>
   <si>
     <t>0.0056,0.0000,0.0014,0.9943</t>
@@ -1339,31 +1339,31 @@
     <t>0.0030,0.0000,0.0006,0.9982</t>
   </si>
   <si>
-    <t>0.0001,0.0000,0.3450,0.6833</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.2032,0.9445</t>
-  </si>
-  <si>
-    <t>0.0029,0.0000,0.0059,0.9895</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.5945,0.4802</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.1420,0.8914</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.1358,0.8599</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.1370,0.7420</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.0640,0.9638</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0634,0.9317</t>
+    <t>0.0001,0.0000,0.3449,0.6836</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.2031,0.9445</t>
+  </si>
+  <si>
+    <t>0.0029,0.0000,0.0059,0.9896</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.5944,0.4805</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.1420,0.8915</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.1357,0.8601</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.1370,0.7422</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0639,0.9638</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.0634,0.9318</t>
   </si>
   <si>
     <t>0.0013,0.0000,0.0136,0.9905</t>
@@ -1375,16 +1375,16 @@
     <t>0.0016,0.0000,0.0361,0.9636</t>
   </si>
   <si>
-    <t>0.0013,0.0000,0.2038,0.8215</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0189,0.9893</t>
-  </si>
-  <si>
-    <t>0.0010,0.0000,0.0577,0.9704</t>
-  </si>
-  <si>
-    <t>0.0022,0.0000,0.0151,0.9937</t>
+    <t>0.0013,0.0000,0.2037,0.8218</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0188,0.9893</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.0576,0.9705</t>
+  </si>
+  <si>
+    <t>0.0022,0.0000,0.0151,0.9938</t>
   </si>
   <si>
     <t>0.0019,0.0000,0.0004,0.9992</t>
@@ -1396,7 +1396,7 @@
     <t>0.0017,0.0000,0.0002,0.9994</t>
   </si>
   <si>
-    <t>0.0021,0.0000,0.0091,0.9930</t>
+    <t>0.0021,0.0000,0.0091,0.9931</t>
   </si>
   <si>
     <t>0.0038,0.0000,0.0018,0.9943</t>
@@ -1405,13 +1405,13 @@
     <t>0.0004,0.0000,0.0105,0.9962</t>
   </si>
   <si>
-    <t>0.0008,0.0000,0.1790,0.8865</t>
+    <t>0.0008,0.0000,0.1788,0.8868</t>
   </si>
   <si>
     <t>0.0022,0.0000,0.0027,0.9958</t>
   </si>
   <si>
-    <t>0.0004,0.0000,0.0975,0.9426</t>
+    <t>0.0004,0.0000,0.0975,0.9427</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.0210,0.9960</t>
@@ -1420,10 +1420,10 @@
     <t>0.0001,0.0000,0.0282,0.9933</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.9585,0.0544</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.2745,0.8516</t>
+    <t>0.0000,0.0000,0.9585,0.0545</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.2744,0.8518</t>
   </si>
   <si>
     <t>0.0026,0.0000,0.0002,0.9990</t>
@@ -1453,31 +1453,31 @@
     <t>0.0016,0.0000,0.0023,0.9973</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.9756,0.0239</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.5774,0.6034</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.2106,0.8422</t>
+    <t>0.0000,0.0000,0.9756,0.0240</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.5773,0.6037</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.2105,0.8423</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9900,0.0081</t>
   </si>
   <si>
-    <t>0.0002,0.0000,0.6480,0.2797</t>
+    <t>0.0002,0.0000,0.6479,0.2800</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9963,0.0012</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.8959,0.1488</t>
+    <t>0.0000,0.0000,0.8958,0.1490</t>
   </si>
   <si>
     <t>0.0006,0.0000,0.0288,0.9885</t>
   </si>
   <si>
-    <t>0.0008,0.0000,0.0119,0.9918</t>
+    <t>0.0008,0.0000,0.0119,0.9919</t>
   </si>
   <si>
     <t>0.0006,0.0000,0.0025,0.9983</t>
@@ -1492,7 +1492,7 @@
     <t>0.0010,0.0000,0.0010,0.9993</t>
   </si>
   <si>
-    <t>0.0018,0.0000,0.0004,0.9993</t>
+    <t>0.0017,0.0000,0.0004,0.9993</t>
   </si>
   <si>
     <t>0.0098,0.0000,0.0004,0.9960</t>
@@ -1501,19 +1501,19 @@
     <t>0.0027,0.0000,0.0002,0.9991</t>
   </si>
   <si>
-    <t>0.0001,0.0000,0.5040,0.5544</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.7457,0.2030</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.8599,0.1014</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.2422,0.7350</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.3053,0.5901</t>
+    <t>0.0001,0.0000,0.5039,0.5548</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.7457,0.2032</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.8598,0.1015</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.2421,0.7352</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.3052,0.5905</t>
   </si>
   <si>
     <t>0.0003,0.0000,0.0004,0.9998</t>
